--- a/informes_data/Primera FEB/2025-26/playoffs/individual/NP_play_by_play_2513252_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/playoffs/individual/NP_play_by_play_2513252_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>L. NWOGBO</t>
+          <t>P. GARINO GULLOTTA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.1572</v>
+        <v>3.3586</v>
       </c>
       <c r="E2" t="n">
-        <v>3.4601</v>
+        <v>1.1018</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6971000000000001</v>
+        <v>2.2568</v>
       </c>
       <c r="G2" t="n">
-        <v>3.172</v>
+        <v>0.6975</v>
       </c>
       <c r="H2" t="n">
-        <v>2.4332</v>
+        <v>0.524</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7388</v>
+        <v>0.1735</v>
       </c>
       <c r="J2" t="n">
-        <v>2.1725</v>
+        <v>-0.2779</v>
       </c>
       <c r="K2" t="n">
-        <v>2.0586</v>
+        <v>-0.7879</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1139</v>
+        <v>0.51</v>
       </c>
       <c r="M2" t="n">
-        <v>0.9995000000000001</v>
+        <v>0.9754</v>
       </c>
       <c r="N2" t="n">
-        <v>0.3746</v>
+        <v>1.3119</v>
       </c>
       <c r="O2" t="n">
-        <v>0.6249</v>
+        <v>-0.3365</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>0.6608000000000001</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1014</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.1014</v>
+        <v>0.6608000000000001</v>
       </c>
       <c r="S2" t="n">
-        <v>1.8415</v>
+        <v>0.9932</v>
       </c>
       <c r="T2" t="n">
-        <v>1.27</v>
+        <v>0.2608</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5715</v>
+        <v>0.7324000000000001</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.8563</v>
+        <v>1.007</v>
       </c>
       <c r="W2" t="n">
         <v>1.1189</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.9752</v>
+        <v>-0.1119</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>P. GARINO GULLOTTA</t>
+          <t>L. NWOGBO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.971</v>
+        <v>3.2858</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9737</v>
+        <v>2.704</v>
       </c>
       <c r="F3" t="n">
-        <v>1.9973</v>
+        <v>0.5818</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6975</v>
+        <v>3.172</v>
       </c>
       <c r="H3" t="n">
-        <v>0.524</v>
+        <v>2.4332</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1735</v>
+        <v>0.7388</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.2779</v>
+        <v>2.1725</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.7879</v>
+        <v>2.0586</v>
       </c>
       <c r="L3" t="n">
-        <v>0.51</v>
+        <v>0.1139</v>
       </c>
       <c r="M3" t="n">
-        <v>0.9754</v>
+        <v>0.9995000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>1.3119</v>
+        <v>0.3746</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.3365</v>
+        <v>0.6249</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6608000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-1.1014</v>
       </c>
       <c r="R3" t="n">
-        <v>0.6608000000000001</v>
+        <v>1.1014</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6057</v>
+        <v>0.9701</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1327</v>
+        <v>0.5139</v>
       </c>
       <c r="U3" t="n">
-        <v>0.473</v>
+        <v>0.4562</v>
       </c>
       <c r="V3" t="n">
-        <v>1.007</v>
+        <v>-0.8563</v>
       </c>
       <c r="W3" t="n">
         <v>1.1189</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.1119</v>
+        <v>-1.9752</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.7022</v>
+        <v>3.0313</v>
       </c>
       <c r="E4" t="n">
-        <v>1.3811</v>
+        <v>1.7967</v>
       </c>
       <c r="F4" t="n">
-        <v>1.3211</v>
+        <v>1.2346</v>
       </c>
       <c r="G4" t="n">
         <v>1.1763</v>
@@ -766,13 +766,13 @@
         <v>1.3216</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2986</v>
+        <v>0.6276</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5843</v>
+        <v>-0.1688</v>
       </c>
       <c r="U4" t="n">
-        <v>0.8829</v>
+        <v>0.7964</v>
       </c>
       <c r="V4" t="n">
         <v>1.007</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.1677</v>
+        <v>2.2446</v>
       </c>
       <c r="E5" t="n">
-        <v>1.0451</v>
+        <v>1.2373</v>
       </c>
       <c r="F5" t="n">
-        <v>1.1227</v>
+        <v>1.0074</v>
       </c>
       <c r="G5" t="n">
         <v>0.0086</v>
@@ -844,13 +844,13 @@
         <v>0.8811</v>
       </c>
       <c r="S5" t="n">
-        <v>1.0886</v>
+        <v>1.1654</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2046</v>
+        <v>0.3968</v>
       </c>
       <c r="U5" t="n">
-        <v>0.884</v>
+        <v>0.7687</v>
       </c>
       <c r="V5" t="n">
         <v>0.1895</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>H. LOPEZ BARRANTES</t>
+          <t>S. GARCIA CALVO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5622</v>
+        <v>1.6565</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7082000000000001</v>
+        <v>0.8754999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>0.854</v>
+        <v>0.7811</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.0753</v>
+        <v>1.883</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5696</v>
+        <v>2.1954</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5057</v>
+        <v>-0.3124</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.5793</v>
+        <v>3.2121</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.6553</v>
+        <v>2.8756</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0759</v>
+        <v>0.3365</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.4959</v>
+        <v>-1.3291</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0857</v>
+        <v>-0.6802</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.5816</v>
+        <v>-0.6489</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.2203</v>
+        <v>-0.6608000000000001</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1014</v>
+        <v>-2.2027</v>
       </c>
       <c r="R6" t="n">
-        <v>0.8811</v>
+        <v>1.5419</v>
       </c>
       <c r="S6" t="n">
-        <v>1.5494</v>
+        <v>0.8089</v>
       </c>
       <c r="T6" t="n">
-        <v>1.27</v>
+        <v>0.2405</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2794</v>
+        <v>0.5683</v>
       </c>
       <c r="V6" t="n">
-        <v>1.3084</v>
+        <v>-0.3745</v>
       </c>
       <c r="W6" t="n">
-        <v>1.1189</v>
+        <v>-0.3745</v>
       </c>
       <c r="X6" t="n">
-        <v>0.1895</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S. GARCIA CALVO</t>
+          <t>H. LOPEZ BARRANTES</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9157</v>
+        <v>1.1603</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2787</v>
+        <v>0.1334</v>
       </c>
       <c r="F7" t="n">
-        <v>0.637</v>
+        <v>1.0269</v>
       </c>
       <c r="G7" t="n">
-        <v>1.883</v>
+        <v>-1.0753</v>
       </c>
       <c r="H7" t="n">
-        <v>2.1954</v>
+        <v>-0.5696</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3124</v>
+        <v>-0.5057</v>
       </c>
       <c r="J7" t="n">
-        <v>3.2121</v>
+        <v>-0.5793</v>
       </c>
       <c r="K7" t="n">
-        <v>2.8756</v>
+        <v>-0.6553</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3365</v>
+        <v>0.0759</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.3291</v>
+        <v>-0.4959</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6802</v>
+        <v>0.0857</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.6489</v>
+        <v>-0.5816</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.6608000000000001</v>
+        <v>-0.2203</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.2027</v>
+        <v>-1.1014</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5419</v>
+        <v>0.8811</v>
       </c>
       <c r="S7" t="n">
-        <v>0.068</v>
+        <v>1.1474</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3562</v>
+        <v>0.6951000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4242</v>
+        <v>0.4523</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.3745</v>
+        <v>1.3084</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.3745</v>
+        <v>1.1189</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>0.1895</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7209</v>
+        <v>0.73</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.8335</v>
+        <v>-0.9397</v>
       </c>
       <c r="F8" t="n">
-        <v>1.5544</v>
+        <v>1.6697</v>
       </c>
       <c r="G8" t="n">
         <v>1.1134</v>
@@ -1078,13 +1078,13 @@
         <v>1.3216</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6736</v>
+        <v>0.6827</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1327</v>
+        <v>0.0265</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5409</v>
+        <v>0.6562</v>
       </c>
       <c r="V8" t="n">
         <v>-0.185</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.8528</v>
+        <v>-0.84</v>
       </c>
       <c r="E9" t="n">
-        <v>0.184</v>
+        <v>0.3121</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.0368</v>
+        <v>-1.1521</v>
       </c>
       <c r="G9" t="n">
         <v>0.0051</v>
@@ -1156,13 +1156,13 @@
         <v>0.8811</v>
       </c>
       <c r="S9" t="n">
-        <v>1.1526</v>
+        <v>1.1654</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2686</v>
+        <v>0.3968</v>
       </c>
       <c r="U9" t="n">
-        <v>0.884</v>
+        <v>0.7687</v>
       </c>
       <c r="V9" t="n">
         <v>-1.7903</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. NIANG</t>
+          <t>L. GIOVANNETTI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.2525</v>
+        <v>-1.1304</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.6326000000000001</v>
+        <v>-1.3195</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.6199</v>
+        <v>0.1891</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.6944</v>
+        <v>-2.495</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.3111</v>
+        <v>-1.2083</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.3834</v>
+        <v>-1.2867</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.0561</v>
+        <v>-1.3507</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.17</v>
+        <v>-0.6456</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1139</v>
+        <v>-0.7050999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.6383</v>
+        <v>-1.1443</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1411</v>
+        <v>-0.5627</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.4973</v>
+        <v>-0.5816</v>
       </c>
       <c r="P10" t="n">
-        <v>0.2203</v>
+        <v>0.6608000000000001</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2203</v>
+        <v>0.6608000000000001</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2217</v>
+        <v>0.7038</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5765</v>
+        <v>0.0312</v>
       </c>
       <c r="U10" t="n">
-        <v>0.7982</v>
+        <v>0.6726</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>L. GIOVANNETTI</t>
+          <t>M. NIANG</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,58 +1267,58 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.437</v>
+        <v>-1.273</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.7991</v>
+        <v>-0.4514</v>
       </c>
       <c r="F11" t="n">
-        <v>0.362</v>
+        <v>-0.8216</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.495</v>
+        <v>-1.6944</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.2083</v>
+        <v>-0.3111</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.2867</v>
+        <v>-1.3834</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.3507</v>
+        <v>-0.0561</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.6456</v>
+        <v>-0.17</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.7050999999999999</v>
+        <v>0.1139</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.1443</v>
+        <v>-1.6383</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.5627</v>
+        <v>-0.1411</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.5816</v>
+        <v>-1.4973</v>
       </c>
       <c r="P11" t="n">
-        <v>0.6608000000000001</v>
+        <v>0.2203</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.6608000000000001</v>
+        <v>0.2203</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3971</v>
+        <v>0.2012</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4484</v>
+        <v>-0.3953</v>
       </c>
       <c r="U11" t="n">
-        <v>0.8455</v>
+        <v>0.5964</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.1516</v>
+        <v>-2.4395</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.8196</v>
+        <v>-4.2228</v>
       </c>
       <c r="F12" t="n">
-        <v>1.668</v>
+        <v>1.7833</v>
       </c>
       <c r="G12" t="n">
         <v>-3.54</v>
@@ -1390,13 +1390,13 @@
         <v>1.5419</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3277</v>
+        <v>0.3843</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8687</v>
+        <v>-0.2719</v>
       </c>
       <c r="U12" t="n">
-        <v>0.5409</v>
+        <v>0.6562</v>
       </c>
       <c r="V12" t="n">
         <v>1.377</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>8.503</v>
+        <v>9.784200000000002</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.0539000000000005</v>
+        <v>1.2274</v>
       </c>
       <c r="F13" t="n">
-        <v>8.556899999999999</v>
+        <v>8.557</v>
       </c>
       <c r="G13" t="n">
         <v>-0.7487999999999992</v>
@@ -1468,13 +1468,13 @@
         <v>11.0136</v>
       </c>
       <c r="S13" t="n">
-        <v>7.569100000000001</v>
+        <v>8.85</v>
       </c>
       <c r="T13" t="n">
-        <v>0.4444999999999997</v>
+        <v>1.7256</v>
       </c>
       <c r="U13" t="n">
-        <v>7.124499999999999</v>
+        <v>7.124400000000001</v>
       </c>
       <c r="V13" t="n">
         <v>1.6828</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.5175</v>
+        <v>2.001</v>
       </c>
       <c r="E14" t="n">
-        <v>1.065</v>
+        <v>0.9479</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4524</v>
+        <v>1.0531</v>
       </c>
       <c r="G14" t="n">
         <v>0.8100000000000001</v>
@@ -1546,13 +1546,13 @@
         <v>1.3216</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.8608</v>
+        <v>-0.3773</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.5641</v>
+        <v>-0.6812</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2967</v>
+        <v>0.3039</v>
       </c>
       <c r="V14" t="n">
         <v>1.5683</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.4441</v>
+        <v>1.7835</v>
       </c>
       <c r="E15" t="n">
-        <v>3</v>
+        <v>2.8829</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.5559</v>
+        <v>-1.0994</v>
       </c>
       <c r="G15" t="n">
         <v>4.3077</v>
@@ -1624,13 +1624,13 @@
         <v>1.3216</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.7007</v>
+        <v>-0.3613</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6281</v>
+        <v>-0.7453</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0726</v>
+        <v>0.384</v>
       </c>
       <c r="V15" t="n">
         <v>-2.1629</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8411</v>
+        <v>0.7258</v>
       </c>
       <c r="E16" t="n">
         <v>0.7806999999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0604</v>
+        <v>-0.0549</v>
       </c>
       <c r="G16" t="n">
         <v>0.7539</v>
@@ -1702,13 +1702,13 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0872</v>
+        <v>-0.0281</v>
       </c>
       <c r="T16" t="n">
         <v>-0.0641</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1512</v>
+        <v>0.0359</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0669</v>
+        <v>-0.0092</v>
       </c>
       <c r="E17" t="n">
         <v>0.0468</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1137</v>
+        <v>-0.0561</v>
       </c>
       <c r="G17" t="n">
         <v>0.6112</v>
@@ -1780,13 +1780,13 @@
         <v>0.6608000000000001</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.8146</v>
+        <v>-0.7569</v>
       </c>
       <c r="T17" t="n">
         <v>-0.4484</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3662</v>
+        <v>-0.3085</v>
       </c>
       <c r="V17" t="n">
         <v>1.6784</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>K. LARSEN</t>
+          <t>E. POLANCO TAVAREZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1937</v>
+        <v>-0.5315</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.4201</v>
+        <v>-1.4603</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2264</v>
+        <v>0.9288</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.9713000000000001</v>
+        <v>-1.4534</v>
       </c>
       <c r="H18" t="n">
-        <v>-3.3732</v>
+        <v>-1.1833</v>
       </c>
       <c r="I18" t="n">
-        <v>2.4019</v>
+        <v>-0.2701</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1864</v>
+        <v>-0.9256</v>
       </c>
       <c r="K18" t="n">
-        <v>-2.3957</v>
+        <v>-0.7684</v>
       </c>
       <c r="L18" t="n">
-        <v>2.5821</v>
+        <v>-0.1572</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.1578</v>
+        <v>-0.5278</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.9775</v>
+        <v>-0.4148</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.1803</v>
+        <v>-0.113</v>
       </c>
       <c r="P18" t="n">
-        <v>1.5419</v>
+        <v>0.8811</v>
       </c>
       <c r="Q18" t="n">
         <v>-0.2203</v>
       </c>
       <c r="R18" t="n">
-        <v>1.7622</v>
+        <v>1.1014</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0153</v>
+        <v>-0.1441</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7562</v>
+        <v>-0.6843</v>
       </c>
       <c r="U18" t="n">
-        <v>0.741</v>
+        <v>0.5402</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.7489</v>
+        <v>0.185</v>
       </c>
       <c r="W18" t="n">
         <v>0.37</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.1189</v>
+        <v>-0.185</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>E. POLANCO TAVAREZ</t>
+          <t>K. LARSEN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.9546</v>
+        <v>-0.6158</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.9289</v>
+        <v>-0.5373</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9744</v>
+        <v>-0.0785</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.4534</v>
+        <v>-0.9713000000000001</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.1833</v>
+        <v>-3.3732</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2701</v>
+        <v>2.4019</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.9256</v>
+        <v>0.1864</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.7684</v>
+        <v>-2.3957</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.1572</v>
+        <v>2.5821</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.5278</v>
+        <v>-1.1578</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4148</v>
+        <v>-0.9775</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.113</v>
+        <v>-0.1803</v>
       </c>
       <c r="P19" t="n">
-        <v>0.8811</v>
+        <v>1.5419</v>
       </c>
       <c r="Q19" t="n">
         <v>-0.2203</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1014</v>
+        <v>1.7622</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5672</v>
+        <v>-0.4374</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.153</v>
+        <v>-0.8734</v>
       </c>
       <c r="U19" t="n">
-        <v>0.5858</v>
+        <v>0.436</v>
       </c>
       <c r="V19" t="n">
-        <v>0.185</v>
+        <v>-0.7489</v>
       </c>
       <c r="W19" t="n">
         <v>0.37</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.185</v>
+        <v>-1.1189</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>U. MENDICOTE RUBIO</t>
+          <t>B. COULIBALY</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.9679</v>
+        <v>-0.9078000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.8287</v>
+        <v>-0.3646</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.1392</v>
+        <v>-0.5432</v>
       </c>
       <c r="G20" t="n">
-        <v>1.5565</v>
+        <v>0.1643</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.2378</v>
+        <v>-0.0222</v>
       </c>
       <c r="I20" t="n">
-        <v>1.7943</v>
+        <v>0.1865</v>
       </c>
       <c r="J20" t="n">
-        <v>1.7903</v>
+        <v>0.1478</v>
       </c>
       <c r="K20" t="n">
-        <v>0.5750999999999999</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="L20" t="n">
-        <v>1.2151</v>
+        <v>0.0759</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.2337</v>
+        <v>0.0165</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.8129999999999999</v>
+        <v>-0.094</v>
       </c>
       <c r="O20" t="n">
-        <v>0.5792</v>
+        <v>0.1106</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.6608000000000001</v>
+        <v>0.4405</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1014</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>0.4405</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.1896</v>
+        <v>-0.4687</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7687</v>
+        <v>-0.5124</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4209</v>
+        <v>0.0438</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.674</v>
+        <v>-1.044</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.7489</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0.07489999999999999</v>
+        <v>-1.044</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>B. COULIBALY</t>
+          <t>U. MENDICOTE RUBIO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.064</v>
+        <v>-0.9559</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.3646</v>
+        <v>-0.8287</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.6994</v>
+        <v>-0.1272</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1643</v>
+        <v>1.5565</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.0222</v>
+        <v>-0.2378</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1865</v>
+        <v>1.7943</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1478</v>
+        <v>1.7903</v>
       </c>
       <c r="K21" t="n">
-        <v>0.07190000000000001</v>
+        <v>0.5750999999999999</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0759</v>
+        <v>1.2151</v>
       </c>
       <c r="M21" t="n">
-        <v>0.0165</v>
+        <v>-0.2337</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.094</v>
+        <v>-0.8129999999999999</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1106</v>
+        <v>0.5792</v>
       </c>
       <c r="P21" t="n">
-        <v>0.4405</v>
+        <v>-0.6608000000000001</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-1.1014</v>
       </c>
       <c r="R21" t="n">
         <v>0.4405</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6249</v>
+        <v>-1.1775</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5124</v>
+        <v>-0.7687</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1124</v>
+        <v>-0.4088</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.044</v>
+        <v>-0.674</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>-0.7489</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.044</v>
+        <v>0.07489999999999999</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.7547</v>
+        <v>-1.4051</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.7946</v>
+        <v>-1.5603</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0399</v>
+        <v>0.1552</v>
       </c>
       <c r="G22" t="n">
         <v>-1.0989</v>
@@ -2170,13 +2170,13 @@
         <v>1.5419</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8761</v>
+        <v>-0.5265</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7687</v>
+        <v>-0.5343</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1075</v>
+        <v>0.0078</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.9695</v>
+        <v>-1.963</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.1592</v>
+        <v>-2.5107</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1897</v>
+        <v>0.5477</v>
       </c>
       <c r="G23" t="n">
         <v>-1.3819</v>
@@ -2248,13 +2248,13 @@
         <v>0.4405</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0907</v>
+        <v>0.09719999999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1157</v>
+        <v>-0.4672</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2064</v>
+        <v>0.5644</v>
       </c>
       <c r="V23" t="n">
         <v>-1.1189</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.0112</v>
+        <v>-2.0401</v>
       </c>
       <c r="E24" t="n">
         <v>-2.5131</v>
       </c>
       <c r="F24" t="n">
-        <v>0.5019</v>
+        <v>0.4731</v>
       </c>
       <c r="G24" t="n">
         <v>-0.8266</v>
@@ -2326,13 +2326,13 @@
         <v>0.8811</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.9644</v>
+        <v>-0.9932</v>
       </c>
       <c r="T24" t="n">
         <v>-0.7046</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2598</v>
+        <v>-0.2886</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.3233</v>
+        <v>-3.0229</v>
       </c>
       <c r="E25" t="n">
         <v>-3.4402</v>
       </c>
       <c r="F25" t="n">
-        <v>0.117</v>
+        <v>0.4173</v>
       </c>
       <c r="G25" t="n">
         <v>-1.7229</v>
@@ -2404,13 +2404,13 @@
         <v>1.1014</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.1334</v>
+        <v>-0.833</v>
       </c>
       <c r="T25" t="n">
         <v>-0.6405999999999999</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.4928</v>
+        <v>-0.1925</v>
       </c>
       <c r="V25" t="n">
         <v>0.6343</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-8.5031</v>
+        <v>-6.941</v>
       </c>
       <c r="E26" t="n">
-        <v>-8.556900000000001</v>
+        <v>-8.556899999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>0.05390000000000029</v>
+        <v>1.6159</v>
       </c>
       <c r="G26" t="n">
         <v>0.7485999999999997</v>
@@ -2482,13 +2482,13 @@
         <v>11.0135</v>
       </c>
       <c r="S26" t="n">
-        <v>-7.569100000000001</v>
+        <v>-6.0068</v>
       </c>
       <c r="T26" t="n">
-        <v>-7.1246</v>
+        <v>-7.1245</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.4445000000000001</v>
+        <v>1.1176</v>
       </c>
       <c r="V26" t="n">
         <v>-1.6827</v>
